--- a/uat-test-plans-reduced30/G2-16257-vertex-search-porter.xlsx
+++ b/uat-test-plans-reduced30/G2-16257-vertex-search-porter.xlsx
@@ -597,7 +597,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>[Reduced ~30% — 7/10 checks retained, lowest-priority sections dropped] 11 UI-testable stories mapped to 10 business checklist checks and 11 coverage rows. 14 backend infrastructure, QA, task, and evaluation items excluded from direct business execution.</t>
+          <t>[Reduced V2 ~30% — 7/10 checks retained; AC and core-case coverage guardrails enforced] 11 UI-testable stories mapped to 10 business checklist checks and 11 coverage rows. 14 backend infrastructure, QA, task, and evaluation items excluded from direct business execution.</t>
         </is>
       </c>
     </row>
@@ -692,7 +692,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>payload_bytes=14751; payload_chars=14749; est_tokens~3688; checklist_rows=7; matrix_rows=11; exploratory_rows=3</t>
+          <t>payload_bytes=14843; payload_chars=14841; est_tokens~3711; checklist_rows=7; matrix_rows=11; exploratory_rows=3</t>
         </is>
       </c>
     </row>
@@ -724,7 +724,7 @@
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
     <col width="50" customWidth="1" min="4" max="4"/>
     <col width="50" customWidth="1" min="5" max="5"/>
     <col width="50" customWidth="1" min="6" max="6"/>
@@ -811,10 +811,10 @@
       <c r="G2" s="5" t="inlineStr"/>
       <c r="H2" s="5" t="inlineStr"/>
     </row>
-    <row r="3" ht="79" customHeight="1">
+    <row r="3" ht="94" customHeight="1">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>UAT-002</t>
+          <t>UAT-004</t>
         </is>
       </c>
       <c r="B3" s="5" t="inlineStr">
@@ -824,204 +824,204 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>Search Results</t>
+          <t>Autocomplete</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>Search results page renders product results for valid terms</t>
+          <t>Autocomplete returns designer/category suggestions with valid destinations</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>Submit multiple valid search terms and confirm dedicated results route, product grid rendering, and stable pagination/loading states.</t>
+          <t>Type partial terms for designers and categories and select suggestions to validate navigation to correct DLP/PLP destinations.</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>Search term submission always reaches the search results page.
-Product grid renders without blocking errors.
-Repeated queries keep page responsive and consistent.</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="inlineStr"/>
-      <c r="H3" s="5" t="inlineStr"/>
-    </row>
-    <row r="4" ht="94" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>UAT-003</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>Kozlova, Nika || External</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>Filters</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>Key filters narrow search results correctly</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>Apply and remove color, designer, category, and price filters on results page and observe product list updates.</t>
-        </is>
-      </c>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t>Filter selections update product results correctly.
-Removing filters restores broader result sets.
-No filter causes broken or empty-state errors when matching products exist.</t>
-        </is>
-      </c>
-      <c r="G4" s="5" t="inlineStr"/>
-      <c r="H4" s="5" t="inlineStr"/>
-    </row>
-    <row r="5" ht="94" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>UAT-004</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>Kozlova, Nika || External</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>Autocomplete</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>Autocomplete returns designer/category suggestions with valid destinations</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr">
-        <is>
-          <t>Type partial terms for designers and categories and select suggestions to validate navigation to correct DLP/PLP destinations.</t>
-        </is>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>Suggestions appear while typing relevant terms.
 Selecting a designer/category suggestion opens a valid destination page.
 No malformed slug or duplicate path fragment appears in URL.</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr"/>
-      <c r="H5" s="5" t="inlineStr"/>
-    </row>
-    <row r="6" ht="94" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr"/>
+      <c r="H3" s="5" t="inlineStr"/>
+    </row>
+    <row r="4" ht="94" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>UAT-005</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>Kozlova, Nika || External</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>Redirects</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>Configured redirect terms route to curated destinations instead of generic product search</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>Search known configured redirect keywords and verify user lands on mapped curated pages instead of generic result listings.</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>Configured redirect terms consistently navigate to curated destination URLs.
 Unconfigured terms continue to standard product search results.
 Redirect handoff does not produce blank/intermediate error pages.</t>
         </is>
       </c>
-      <c r="G6" s="5" t="inlineStr"/>
-      <c r="H6" s="5" t="inlineStr"/>
-    </row>
-    <row r="7" ht="94" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>UAT-006</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr"/>
+      <c r="H4" s="5" t="inlineStr"/>
+    </row>
+    <row r="5" ht="79" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>UAT-007</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>Kozlova, Nika || External</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>Redirect Safety</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>Manual/custom PLP terms do not trigger unwanted redirects</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>Search terms associated with manual/custom PLP rules and confirm search results remain in standard results flow where redirect exclusion is expected.</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>Excluded manual/custom PLP terms do not redirect unexpectedly.
-Search results are shown normally for excluded terms.
-Behavior is consistent across repeated attempts.</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr"/>
-      <c r="H7" s="5" t="inlineStr"/>
-    </row>
-    <row r="8" ht="79" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>UAT-007</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>Kozlova, Nika || External</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>Internal Match Logic</t>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>Match-slug based internal redirects and FE consumption are consistent</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>Test terms expected to produce match-slug behavior and confirm FE redirects correctly when match exists and remains on results when not matched.</t>
         </is>
       </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>Matched terms trigger the intended redirect behavior.
 Non-matched terms remain on product results flow.
 No redirect loop or partial load occurs.</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr"/>
+      <c r="H5" s="5" t="inlineStr"/>
+    </row>
+    <row r="6" ht="64" customHeight="1">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>UAT-008</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Kozlova, Nika || External</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Brand Coverage</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Search behavior parity is maintained across NAP and MRP</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Run core search, filter, autocomplete, and redirect checks on both NAP and MRP acceptance environments.</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>Core search flow works on both brands.
+Known brand-specific datasets do not break shared behavior.
+No cross-brand routing anomalies appear.</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr"/>
+      <c r="H6" s="5" t="inlineStr"/>
+    </row>
+    <row r="7" ht="94" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>UAT-009</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Kozlova, Nika || External</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Navigation Continuity</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Back and forward browser/app navigation remains coherent through search journey</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Perform multi-step journey (search entry -&gt; autocomplete/submit -&gt; results -&gt; product/listing -&gt; back/forward) and verify state continuity.</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>Back navigation returns to expected previous screen/state.
+Forward navigation replays route without broken context.
+Search state does not reset unexpectedly unless intended.</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr"/>
+      <c r="H7" s="5" t="inlineStr"/>
+    </row>
+    <row r="8" ht="94" customHeight="1">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>UAT-010</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Kozlova, Nika || External</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Regression Sanity</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>Vertex-based search does not regress baseline discoverability behavior</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>Run a short end-to-end journey from query to landing page/product page for several terms and verify outcomes remain relevant and actionable.</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>Users can discover products or curated pages for representative terms.
+Journey completes without major UX regressions.
+Failure cases are limited to known documented gaps.</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr"/>
@@ -1046,7 +1046,7 @@
     <col width="35" customWidth="1" min="3" max="3"/>
     <col width="50" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="24" customWidth="1" min="9" max="9"/>
@@ -1139,7 +1139,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>UAT-001</t>
+          <t>UAT-001, UAT-009</t>
         </is>
       </c>
       <c r="G2" s="5" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>UAT-002</t>
+          <t>UAT-010</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>UAT-003</t>
+          <t>UAT-010</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>UAT-004</t>
+          <t>UAT-004, UAT-008</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
@@ -1367,7 +1367,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>UAT-004</t>
+          <t>UAT-004, UAT-010</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>UAT-006, UAT-007</t>
+          <t>UAT-007</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>UAT-005, UAT-007</t>
+          <t>UAT-005, UAT-007, UAT-009</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
@@ -1709,7 +1709,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>UAT-004</t>
+          <t>UAT-004, UAT-008, UAT-010</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">

--- a/uat-test-plans-reduced30/G2-16257-vertex-search-porter.xlsx
+++ b/uat-test-plans-reduced30/G2-16257-vertex-search-porter.xlsx
@@ -597,7 +597,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>[Reduced V2 ~30% — 7/10 checks retained; AC and core-case coverage guardrails enforced] 11 UI-testable stories mapped to 10 business checklist checks and 11 coverage rows. 14 backend infrastructure, QA, task, and evaluation items excluded from direct business execution.</t>
+          <t>[Reduced V2 ~30% — 7/10 checks retained; AC coverage guardrail enforced] 11 UI-testable stories mapped to 10 business checklist checks and 11 coverage rows. 14 backend infrastructure, QA, task, and evaluation items excluded from direct business execution.</t>
         </is>
       </c>
     </row>
@@ -692,7 +692,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>payload_bytes=14843; payload_chars=14841; est_tokens~3711; checklist_rows=7; matrix_rows=11; exploratory_rows=3</t>
+          <t>payload_bytes=14828; payload_chars=14826; est_tokens~3707; checklist_rows=7; matrix_rows=11; exploratory_rows=3</t>
         </is>
       </c>
     </row>
